--- a/apps/vione_app_fe/public/docs/TIEN_DO_CONG_VIEC_VIONE.xlsx
+++ b/apps/vione_app_fe/public/docs/TIEN_DO_CONG_VIEC_VIONE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="86">
   <si>
     <t>STT</t>
   </si>
@@ -185,13 +185,97 @@
   </si>
   <si>
     <t>Toàn bộ ca kiểm thử Pass 100%</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>Phân Quyền Phòng Ban Chuyên Trách (Department-based RBAC)</t>
+  </si>
+  <si>
+    <t>Solution Architect &amp; Fullstack Lead</t>
+  </si>
+  <si>
+    <t>Khối -&gt; Phòng ban -&gt; Nhóm chuyên trách (vione_community_departments). Kiểm soát 5 cờ quyền: canAssign, canAccept, canReport, canHandover, canMeet. Department Guard bảo mật dữ liệu theo phòng ban.</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Cơ Chế Bàn Giao Công Việc Tự Động (Auto-Handover Engine)</t>
+  </si>
+  <si>
+    <t>Senior Backend Dev &amp; Mobile Lead</t>
+  </si>
+  <si>
+    <t>Gom và chuyển giao hàng loạt công việc (tasks), khách hàng (CRM customers), cơ hội (deals) khi luân chuyển hoặc thôi việc. Tự động sinh biên bản bàn giao, phát thông báo Push/In-app, lưu vết audit trail handover_history.</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>Mô Hình Cộng Đồng Hợp Nhất &amp; Gói Dùng Thử 30 Ngày (Unified Community &amp; 30-Day Subscription)</t>
+  </si>
+  <si>
+    <t>Product Owner &amp; Frontend Lead</t>
+  </si>
+  <si>
+    <t>Hợp nhất 2 mô hình cộng đồng (Nội bộ &amp; B2B) thành 1 mô hình toàn năng duy nhất (tasks, supervision, opportunities, news, events, members). Gating phân hệ giao việc tại Trang chủ (chỉ hiện khi có gói hoặc dùng thử 30 ngày free). Thẻ CTA Champagne Gold và form khởi tạo 1-chạm.</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>Họp Ban Trực Tuyến 1-Chạm (Instant Department Meeting - C-Level Room)</t>
+  </si>
+  <si>
+    <t>Mobile Dev &amp; WebRTC Engineer</t>
+  </si>
+  <si>
+    <t>Nút họp ban 1-chạm mạ vàng trên thanh công cụ điều hành công việc. Khởi tạo tức thì phòng họp WebRTC C-Level bảo mật cao, tự động gửi thông báo triệu tập khẩn cấp đến nhân sự phòng ban.</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>Import &amp; Export Đa Định Dạng (Excel &amp; Word for Assigner &amp; Assignee)</t>
+  </si>
+  <si>
+    <t>Backend &amp; Frontend Dev</t>
+  </si>
+  <si>
+    <t>Người giao việc: Nạp công việc hàng loạt từ tệp .xlsx/.csv và đề án nhiệm vụ từ .docx. Người nhận việc: Đính kèm đồng thời báo cáo Word và bảng tính số liệu Excel khi nghiệm thu công việc.</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>Màn Đăng Nhập CRM Tĩnh C-Level &amp; Bộ Lọc Trạng Thái Toàn Diện (Dashboard &amp; Marketplace)</t>
+  </si>
+  <si>
+    <t>UI/UX Lead &amp; Senior Frontend Dev</t>
+  </si>
+  <si>
+    <t>Triệt tiêu 100% animation xoay vòng gây phân tâm, áp dụng kiến trúc tĩnh 2 cột mạ vàng sang trọng. Trang bị bộ lọc trạng thái đa chiều (Status Filter Tabs) kèm badge đếm số lượng thời gian thực trên C-Level Dashboard và Sàn Marketplace.</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>Đồng Bộ Hoàn Toàn Chức Năng ViOne PWA Với ViOne Native App &amp; Cân Đối UI/UX</t>
+  </si>
+  <si>
+    <t>Mobile Lead &amp; Senior UI/UX Designer</t>
+  </si>
+  <si>
+    <t>Đồng bộ 100% tính năng giữa PWA (/connect-app) và Native App (apps/mobile_vione). Cân đối chuẩn xác bố trí text, icon, typography, safe area insets (Dynamic Island / Gesture Nav) trên 4 tabs chính (Home, Network, Community, Me), nút V trung tâm (VActionSheet), PostMomentModal, CardScanReviewModal, ViOneVoiceAssistantModal.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -202,6 +286,10 @@
     <font>
       <b/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -211,7 +299,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -219,13 +307,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -916,8 +1025,190 @@
         <v>57</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="2">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2">
+        <v>100</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2">
+        <v>100</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2">
+        <v>100</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="2">
+        <v>100</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2">
+        <v>100</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>